--- a/data/trans_orig/IP07C09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61118</t>
+          <t>60939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>43474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60856</t>
+          <t>60170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91666</t>
+          <t>90892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117298</t>
+          <t>115787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42167</t>
+          <t>42568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58949</t>
+          <t>59877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68142</t>
+          <t>67189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96625</t>
+          <t>96972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121913</t>
+          <t>123123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61907</t>
+          <t>62699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>83670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73363</t>
+          <t>73998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95467</t>
+          <t>95795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141503</t>
+          <t>143222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171008</t>
+          <t>172855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76799</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98853</t>
+          <t>98205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73118</t>
+          <t>73643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95223</t>
+          <t>95385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158616</t>
+          <t>158511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188839</t>
+          <t>187181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>24100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>112035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138787</t>
+          <t>138598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123651</t>
+          <t>122870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149810</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241035</t>
+          <t>240837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281190</t>
+          <t>280067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152734</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>156832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261406</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299855</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69822</t>
+          <t>70318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89434</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74410</t>
+          <t>73370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94367</t>
+          <t>93995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149981</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178054</t>
+          <t>178183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>45737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65466</t>
+          <t>64974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>64697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95742</t>
+          <t>95878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122637</t>
+          <t>124436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31807</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3495,47 +3495,47 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71690</t>
+          <t>72692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92741</t>
+          <t>95035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86236</t>
+          <t>87069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107291</t>
+          <t>108252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164537</t>
+          <t>166342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194430</t>
+          <t>194861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>48732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70207</t>
+          <t>70119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>47938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68771</t>
+          <t>69178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104201</t>
+          <t>104158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132878</t>
+          <t>133380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17115</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146711</t>
+          <t>149445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>179201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165415</t>
+          <t>166109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196914</t>
+          <t>194846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323956</t>
+          <t>324900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>366658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>127750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125690</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207592</t>
+          <t>207175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246931</t>
+          <t>244762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98485</t>
+          <t>98408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120571</t>
+          <t>119928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99538</t>
+          <t>100518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121305</t>
+          <t>122916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204570</t>
+          <t>205827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235366</t>
+          <t>235416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45986</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66062</t>
+          <t>67639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35770</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86335</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115930</t>
+          <t>116416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36788</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83790</t>
+          <t>84394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106010</t>
+          <t>105805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85539</t>
+          <t>85065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106223</t>
+          <t>106674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173108</t>
+          <t>175435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204661</t>
+          <t>206125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>40838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61192</t>
+          <t>60029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71244</t>
+          <t>70878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97206</t>
+          <t>96542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>126355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21681</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>39282</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188591</t>
+          <t>188942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219781</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192969</t>
+          <t>192035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221476</t>
+          <t>221772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>390803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434426</t>
+          <t>434316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93190</t>
+          <t>91155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121084</t>
+          <t>121751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>91284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>120261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190006</t>
+          <t>191305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230938</t>
+          <t>231753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70496</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la menor en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>51655</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61582</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>52644</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60939</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44229</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>61905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51655</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>43474</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60170</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90892</t>
+          <t>91500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115787</t>
+          <t>116334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58846</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49596</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67196</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50833</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42568</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59877</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41880</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>59243</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>45,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58846</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49908</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67189</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96972</t>
+          <t>98142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123123</t>
+          <t>122440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11505</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17316</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6910</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3281</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12196</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12043</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11505</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6811</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18116</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26199</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5012</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4662</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4055</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122814</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122814</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122814</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122814</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122814</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84608</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73365</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95674</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>72488</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62699</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83670</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>62981</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>83585</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84608</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73998</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95795</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143222</t>
+          <t>140872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172855</t>
+          <t>172283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84044</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73376</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>88338</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76542</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98205</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78175</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>98944</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>49,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84044</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73643</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95385</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158511</t>
+          <t>156575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187181</t>
+          <t>188168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15373</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9929</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16023</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10497</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10376</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23553</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,99%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15373</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10469</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>22817</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24100</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40847</t>
+          <t>40598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1358</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4708</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4928</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184704</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184704</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184704</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178206</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178206</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178206</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184704</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184704</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>136262</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>122530</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>150785</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>125131</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>112035</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>138598</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>112207</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>139499</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>43,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>136262</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>122870</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>149748</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240837</t>
+          <t>241068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>280067</t>
+          <t>280178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142890</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>129134</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>158663</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>139170</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125639</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>153669</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>123787</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>153390</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>142890</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>129111</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>156832</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>46,47%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264766</t>
+          <t>263215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303881</t>
+          <t>301797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26878</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19680</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>36064</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>22932</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16542</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31882</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>16318</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>30869</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>26878</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>19792</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>35501</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2682</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7063</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6751</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>307518</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>307518</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>307518</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>289916</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>307518</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>307518</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>307518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la menor en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83938</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74171</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>94471</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>80305</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>70318</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>90360</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>70317</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>89775</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>47,37%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>83938</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73370</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93995</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,61%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>47,73%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149481</t>
+          <t>150178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178183</t>
+          <t>177815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53546</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43499</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55233</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45737</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64974</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45339</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64413</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53546</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45011</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64697</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95878</t>
+          <t>96462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124436</t>
+          <t>122846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11618</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6555</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18122</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11648</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7395</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18228</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11618</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7050</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18090</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31910</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1251</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3862</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4229</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6529</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3450,92 +3450,92 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5437</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>153705</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>153705</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>153705</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>148438</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>148438</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>148438</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>153705</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>153705</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>153705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>97602</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86425</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106344</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82945</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72692</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95035</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>71708</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>92460</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>97602</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87069</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>108252</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>57,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166342</t>
+          <t>165657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194861</t>
+          <t>194921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -3798,67 +3798,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>58448</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49574</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69171</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>59954</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48732</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70119</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>51330</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71113</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,96%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58448</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47938</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69178</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104158</t>
+          <t>104160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133380</t>
+          <t>132775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10769</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6601</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12788</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19640</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7710</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19135</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10769</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6423</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17104</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6769</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6473</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4139</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4716</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4498</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1654</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9257</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9245</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169384</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169384</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169384</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169384</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169384</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>181540</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>166951</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>196644</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>163250</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>149445</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>179201</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>148770</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>176827</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>181540</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>166109</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>194846</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324900</t>
+          <t>326330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366658</t>
+          <t>366328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>111994</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>98060</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127229</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>115188</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>100128</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>127750</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100891</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>129914</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>111994</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>97458</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>126446</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207175</t>
+          <t>207712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244762</t>
+          <t>245072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22387</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15329</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>24436</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17531</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>33132</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17110</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>32379</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>22387</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>15998</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30337</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58757</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3275</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7136</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7292</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3771</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7714</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7608</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4498</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9334</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7416</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>323089</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>323089</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>323089</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310647</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310647</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310647</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>323089</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>323089</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>323089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la menor en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>111552</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100180</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>121537</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>109573</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98408</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>119928</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>98086</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>119902</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>60,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>111552</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>100518</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>122916</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205827</t>
+          <t>205759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235416</t>
+          <t>234617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44977</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35202</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55962</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46957</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67639</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46319</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66336</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44977</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35161</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54863</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>87425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116416</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16089</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23894</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11204</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6779</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17411</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>17847</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,22%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16089</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10286</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23721</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>36193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2128</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5718</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6544</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6587</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5726,74 +5726,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4876</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4888</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5314</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177356</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177356</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177356</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>177356</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177356</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>177356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95737</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84843</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106990</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>94662</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84394</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105805</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>83880</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>104707</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>57,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>95737</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>85065</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>106674</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175435</t>
+          <t>175153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206125</t>
+          <t>207045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60273</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49818</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71070</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>50191</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40838</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60029</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>61040</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>30,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>60273</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70878</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,6%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96542</t>
+          <t>94069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126355</t>
+          <t>124050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11792</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6911</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18555</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17859</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11738</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25304</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11811</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26333</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11792</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7318</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19169</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>39020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -6295,74 +6295,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4763</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1479</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5293</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6413,102 +6413,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4419</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4307</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169288</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169288</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169288</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169288</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169288</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>207289</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>191234</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>222004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>204235</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>188942</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>219907</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>188165</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>218602</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>207289</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>192035</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>221772</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390803</t>
+          <t>390091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434316</t>
+          <t>432677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,55%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>105251</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>91543</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119165</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>106153</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>91155</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121751</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>92311</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121135</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>105251</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>91284</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>120261</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191305</t>
+          <t>190845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231753</t>
+          <t>232492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27882</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19898</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>37726</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>29063</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>21560</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>38650</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>21023</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>39546</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,42%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>27882</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20120</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>36633</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>45542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6982,67 +6982,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8173</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>3606</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8043</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7604</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3733</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8123</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2490</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6121</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>346644</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>346644</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>346644</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>345054</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>345054</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>345054</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>346644</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>346644</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>346644</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
